--- a/sheets/조재수대금교본/검수/울고넘는 박달재2.xlsx
+++ b/sheets/조재수대금교본/검수/울고넘는 박달재2.xlsx
@@ -2307,17 +2307,9 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
@@ -2334,17 +2326,9 @@
         </is>
       </c>
       <c r="C5" s="23"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="23"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="23"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
@@ -2357,8 +2341,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C6" s="24"/>
@@ -2400,8 +2383,7 @@
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="I7" s="22"/>
@@ -2411,7 +2393,7 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="C8" s="23"/>
@@ -2431,7 +2413,7 @@
       <c r="G8" s="23"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ʒ
+          <t xml:space="preserve">仲
 太黃</t>
         </is>
       </c>
@@ -2542,14 +2524,13 @@
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-ﾉ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -2561,8 +2542,7 @@
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-ﾉ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I13" s="23"/>
@@ -2579,14 +2559,13 @@
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ʒ
+          <t xml:space="preserve">太
 黃太</t>
         </is>
       </c>
@@ -2609,7 +2588,7 @@
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E15" s="22"/>
@@ -2657,11 +2636,7 @@
         </is>
       </c>
       <c r="C18" s="24"/>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D18" s="21"/>
       <c r="E18" s="24"/>
       <c r="F18" s="21"/>
       <c r="G18" s="24"/>

--- a/sheets/조재수대금교본/검수/울고넘는 박달재2.xlsx
+++ b/sheets/조재수대금교본/검수/울고넘는 박달재2.xlsx
@@ -2307,9 +2307,17 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
-      <c r="D4" s="21"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
@@ -2326,9 +2334,17 @@
         </is>
       </c>
       <c r="C5" s="23"/>
-      <c r="D5" s="21"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E5" s="23"/>
-      <c r="F5" s="21"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G5" s="23"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
@@ -2393,7 +2409,7 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="C8" s="23"/>
@@ -2413,7 +2429,7 @@
       <c r="G8" s="23"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
+          <t xml:space="preserve">仲ʒ
 太黃</t>
         </is>
       </c>
@@ -2524,13 +2540,14 @@
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+ﾉ</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -2542,7 +2559,8 @@
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+ﾉ</t>
         </is>
       </c>
       <c r="I13" s="23"/>
@@ -2565,7 +2583,7 @@
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太ʒ
 黃太</t>
         </is>
       </c>
@@ -2588,7 +2606,7 @@
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="E15" s="22"/>

--- a/sheets/조재수대금교본/검수/울고넘는 박달재2.xlsx
+++ b/sheets/조재수대금교본/검수/울고넘는 박달재2.xlsx
@@ -2244,20 +2244,20 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="61.54" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="68.7" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="I3" s="22"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="68.7" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="68.7" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="I5" s="23"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="68.7" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I6" s="24"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="68.7" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="I7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="68.7" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I8" s="23"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="68.7" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="I9" s="23"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="68.7" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -2473,7 +2473,7 @@
       <c r="H10" s="21"/>
       <c r="I10" s="24"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="68.7" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="I11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="68.7" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="I12" s="23"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="68.7" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="68.7" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="I14" s="24"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="68.7" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="I15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="68.7" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -2634,7 +2634,7 @@
       <c r="H16" s="21"/>
       <c r="I16" s="23"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="68.7" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -2645,7 +2645,7 @@
       <c r="H17" s="21"/>
       <c r="I17" s="23"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="68.7" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -2667,6 +2667,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="65"/>
 </worksheet>
 </file>